--- a/tame_output/ON/bt/strategyON_20231102.xlsx
+++ b/tame_output/ON/bt/strategyON_20231102.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -666,12 +666,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>85.9%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-157.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>132.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.2%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1768"/>
+  <dimension ref="A1:G1769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059920372423617</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42190,6 +42190,29 @@
       </c>
       <c r="G1768" t="n">
         <v>4.333591034636732</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B1769" t="n">
+        <v>3.094867527064018</v>
+      </c>
+      <c r="C1769" t="n">
+        <v>3.049962823512704</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>1.540634880613003</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>3.665860351444158</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>2.164437302312861</v>
+      </c>
+      <c r="G1769" t="n">
+        <v>4.348625204900422</v>
       </c>
     </row>
   </sheetData>
